--- a/확률및통계/13주차/ch13_height_weight.xlsx
+++ b/확률및통계/13주차/ch13_height_weight.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcpe1\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2026_class\확률및통계\13주차\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79E0789-AA63-48F4-A1FD-CDD0DE9B8889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C5A8B8-0F58-48D3-BA1A-CC89E93548B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -207,20 +207,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2059,16 +2056,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>298450</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>393700</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>298450</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>387350</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2095,16 +2092,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>298450</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>254000</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>298450</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>254000</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2627,10 +2624,10 @@
       <c r="B28">
         <v>55</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F28" s="4"/>
+      <c r="F28" s="3"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29">
@@ -2639,10 +2636,10 @@
       <c r="B29">
         <v>64</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" t="s">
         <v>4</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29">
         <v>0.73500055860907298</v>
       </c>
     </row>
@@ -2653,10 +2650,10 @@
       <c r="B30">
         <v>59</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" t="s">
         <v>5</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30">
         <v>0.54022582115564932</v>
       </c>
     </row>
@@ -2667,10 +2664,10 @@
       <c r="B31">
         <v>55</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" t="s">
         <v>6</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31">
         <v>0.53084267464862178</v>
       </c>
     </row>
@@ -2681,10 +2678,10 @@
       <c r="B32">
         <v>38</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" t="s">
         <v>7</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32">
         <v>6.6942640958139874</v>
       </c>
     </row>
@@ -2695,10 +2692,10 @@
       <c r="B33">
         <v>45</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="1">
         <v>51</v>
       </c>
     </row>
@@ -2728,20 +2725,20 @@
       <c r="B36">
         <v>50</v>
       </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3" t="s">
+      <c r="E36" s="2"/>
+      <c r="F36" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G36" s="3" t="s">
+      <c r="G36" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H36" s="3" t="s">
+      <c r="H36" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I36" s="3" t="s">
+      <c r="I36" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J36" s="3" t="s">
+      <c r="J36" s="2" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2752,22 +2749,22 @@
       <c r="B37">
         <v>63</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" t="s">
         <v>10</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37">
         <v>1</v>
       </c>
-      <c r="G37" s="1">
+      <c r="G37">
         <v>2580.0761511867413</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H37">
         <v>2580.0761511867413</v>
       </c>
-      <c r="I37" s="1">
+      <c r="I37">
         <v>57.574057993344127</v>
       </c>
-      <c r="J37" s="1">
+      <c r="J37">
         <v>8.1978941550294546E-10</v>
       </c>
     </row>
@@ -2778,20 +2775,18 @@
       <c r="B38">
         <v>71</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" t="s">
         <v>11</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38">
         <v>49</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G38">
         <v>2195.8454174407088</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H38">
         <v>44.813171784504263</v>
       </c>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
     </row>
     <row r="39" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A39">
@@ -2800,18 +2795,18 @@
       <c r="B39">
         <v>52</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="1">
         <v>50</v>
       </c>
-      <c r="G39" s="2">
+      <c r="G39" s="1">
         <v>4775.9215686274501</v>
       </c>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
     </row>
     <row r="40" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A40">
@@ -2828,29 +2823,29 @@
       <c r="B41">
         <v>52</v>
       </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3" t="s">
+      <c r="E41" s="2"/>
+      <c r="F41" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G41" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="H41" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I41" s="3" t="s">
+      <c r="I41" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J41" s="3" t="s">
+      <c r="J41" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K41" s="3" t="s">
+      <c r="K41" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L41" s="3" t="s">
+      <c r="L41" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M41" s="3" t="s">
+      <c r="M41" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -2861,31 +2856,31 @@
       <c r="B42">
         <v>61</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" t="s">
         <v>13</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42">
         <v>-100.17827165850804</v>
       </c>
-      <c r="G42" s="1">
+      <c r="G42">
         <v>20.916626091506846</v>
       </c>
-      <c r="H42" s="1">
+      <c r="H42">
         <v>-4.7894087325673054</v>
       </c>
-      <c r="I42" s="1">
+      <c r="I42">
         <v>1.586488036556069E-5</v>
       </c>
-      <c r="J42" s="1">
+      <c r="J42">
         <v>-142.21180549629153</v>
       </c>
-      <c r="K42" s="1">
+      <c r="K42">
         <v>-58.144737820724544</v>
       </c>
-      <c r="L42" s="1">
+      <c r="L42">
         <v>-142.21180549629153</v>
       </c>
-      <c r="M42" s="1">
+      <c r="M42">
         <v>-58.144737820724544</v>
       </c>
     </row>
@@ -2896,31 +2891,31 @@
       <c r="B43">
         <v>65</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="1">
         <v>0.94452655701248789</v>
       </c>
-      <c r="G43" s="2">
+      <c r="G43" s="1">
         <v>0.12448033629029709</v>
       </c>
-      <c r="H43" s="2">
+      <c r="H43" s="1">
         <v>7.5877571121737981</v>
       </c>
-      <c r="I43" s="2">
+      <c r="I43" s="1">
         <v>8.1978941550295724E-10</v>
       </c>
-      <c r="J43" s="2">
+      <c r="J43" s="1">
         <v>0.69437395569398674</v>
       </c>
-      <c r="K43" s="2">
+      <c r="K43" s="1">
         <v>1.194679158330989</v>
       </c>
-      <c r="L43" s="2">
+      <c r="L43" s="1">
         <v>0.69437395569398674</v>
       </c>
-      <c r="M43" s="2">
+      <c r="M43" s="1">
         <v>1.194679158330989</v>
       </c>
     </row>
@@ -2987,19 +2982,19 @@
       <c r="B49">
         <v>59</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E49" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="F49" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="G49" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I49" s="3" t="s">
+      <c r="I49" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J49" s="3" t="s">
+      <c r="J49" s="2" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3010,19 +3005,19 @@
       <c r="B50">
         <v>55</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50">
         <v>1</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50">
         <v>70.781035160752282</v>
       </c>
-      <c r="G50" s="1">
+      <c r="G50">
         <v>7.2189648392477181</v>
       </c>
-      <c r="I50" s="1">
+      <c r="I50">
         <v>0.98039215686274506</v>
       </c>
-      <c r="J50" s="1">
+      <c r="J50">
         <v>38</v>
       </c>
     </row>
@@ -3033,19 +3028,19 @@
       <c r="B51">
         <v>74</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E51">
         <v>2</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F51">
         <v>51.890504020502505</v>
       </c>
-      <c r="G51" s="1">
+      <c r="G51">
         <v>-2.8905040205025045</v>
       </c>
-      <c r="I51" s="1">
+      <c r="I51">
         <v>2.9411764705882351</v>
       </c>
-      <c r="J51" s="1">
+      <c r="J51">
         <v>45</v>
       </c>
     </row>
@@ -3056,835 +3051,835 @@
       <c r="B52">
         <v>74</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E52">
         <v>3</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52">
         <v>60.391243033614899</v>
       </c>
-      <c r="G52" s="1">
+      <c r="G52">
         <v>-8.3912430336148986</v>
       </c>
-      <c r="I52" s="1">
+      <c r="I52">
         <v>4.901960784313725</v>
       </c>
-      <c r="J52" s="1">
+      <c r="J52">
         <v>45</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="E53" s="1">
+      <c r="E53">
         <v>4</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53">
         <v>50.94597746349001</v>
       </c>
-      <c r="G53" s="1">
+      <c r="G53">
         <v>2.05402253650999</v>
       </c>
-      <c r="I53" s="1">
+      <c r="I53">
         <v>6.8627450980392153</v>
       </c>
-      <c r="J53" s="1">
+      <c r="J53">
         <v>46</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="E54" s="1">
+      <c r="E54">
         <v>5</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F54">
         <v>49.056924349465049</v>
       </c>
-      <c r="G54" s="1">
+      <c r="G54">
         <v>0.94307565053495068</v>
       </c>
-      <c r="I54" s="1">
+      <c r="I54">
         <v>8.8235294117647047</v>
       </c>
-      <c r="J54" s="1">
+      <c r="J54">
         <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="E55" s="1">
+      <c r="E55">
         <v>6</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55">
         <v>58.502189919589938</v>
       </c>
-      <c r="G55" s="1">
+      <c r="G55">
         <v>-1.502189919589938</v>
       </c>
-      <c r="I55" s="1">
+      <c r="I55">
         <v>10.784313725490195</v>
       </c>
-      <c r="J55" s="1">
+      <c r="J55">
         <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="E56" s="1">
+      <c r="E56">
         <v>7</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F56">
         <v>52.835030577514999</v>
       </c>
-      <c r="G56" s="1">
+      <c r="G56">
         <v>0.1649694224850009</v>
       </c>
-      <c r="I56" s="1">
+      <c r="I56">
         <v>12.745098039215685</v>
       </c>
-      <c r="J56" s="1">
+      <c r="J56">
         <v>48</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="E57" s="1">
+      <c r="E57">
         <v>8</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F57">
         <v>68.891982046727293</v>
       </c>
-      <c r="G57" s="1">
+      <c r="G57">
         <v>-14.891982046727293</v>
       </c>
-      <c r="I57" s="1">
+      <c r="I57">
         <v>14.705882352941176</v>
       </c>
-      <c r="J57" s="1">
+      <c r="J57">
         <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="E58" s="1">
+      <c r="E58">
         <v>9</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58">
         <v>72.670088274777243</v>
       </c>
-      <c r="G58" s="1">
+      <c r="G58">
         <v>-1.6700882747772425</v>
       </c>
-      <c r="I58" s="1">
+      <c r="I58">
         <v>16.666666666666664</v>
       </c>
-      <c r="J58" s="1">
+      <c r="J58">
         <v>49</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="E59" s="1">
+      <c r="E59">
         <v>10</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59">
         <v>67.947455489714798</v>
       </c>
-      <c r="G59" s="1">
+      <c r="G59">
         <v>5.0525445102852018</v>
       </c>
-      <c r="I59" s="1">
+      <c r="I59">
         <v>18.627450980392155</v>
       </c>
-      <c r="J59" s="1">
+      <c r="J59">
         <v>50</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="E60" s="1">
+      <c r="E60">
         <v>11</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60">
         <v>61.335769590627393</v>
       </c>
-      <c r="G60" s="1">
+      <c r="G60">
         <v>-6.3357695906273932</v>
       </c>
-      <c r="I60" s="1">
+      <c r="I60">
         <v>20.588235294117645</v>
       </c>
-      <c r="J60" s="1">
+      <c r="J60">
         <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="E61" s="1">
+      <c r="E61">
         <v>12</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61">
         <v>67.002928932702332</v>
       </c>
-      <c r="G61" s="1">
+      <c r="G61">
         <v>5.9970710672976679</v>
       </c>
-      <c r="I61" s="1">
+      <c r="I61">
         <v>22.549019607843135</v>
       </c>
-      <c r="J61" s="1">
+      <c r="J61">
         <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="E62" s="1">
+      <c r="E62">
         <v>13</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62">
         <v>53.779557134527494</v>
       </c>
-      <c r="G62" s="1">
+      <c r="G62">
         <v>-2.7795571345274936</v>
       </c>
-      <c r="I62" s="1">
+      <c r="I62">
         <v>24.509803921568626</v>
       </c>
-      <c r="J62" s="1">
+      <c r="J62">
         <v>51</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="E63" s="1">
+      <c r="E63">
         <v>14</v>
       </c>
-      <c r="F63" s="1">
+      <c r="F63">
         <v>49.056924349465049</v>
       </c>
-      <c r="G63" s="1">
+      <c r="G63">
         <v>3.9430756505349507</v>
       </c>
-      <c r="I63" s="1">
+      <c r="I63">
         <v>26.470588235294116</v>
       </c>
-      <c r="J63" s="1">
+      <c r="J63">
         <v>52</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="E64" s="1">
+      <c r="E64">
         <v>15</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64">
         <v>50.94597746349001</v>
       </c>
-      <c r="G64" s="1">
+      <c r="G64">
         <v>14.05402253650999</v>
       </c>
-      <c r="I64" s="1">
+      <c r="I64">
         <v>28.431372549019606</v>
       </c>
-      <c r="J64" s="1">
+      <c r="J64">
         <v>52</v>
       </c>
     </row>
     <row r="65" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E65" s="1">
+      <c r="E65">
         <v>16</v>
       </c>
-      <c r="F65" s="1">
+      <c r="F65">
         <v>50.94597746349001</v>
       </c>
-      <c r="G65" s="1">
+      <c r="G65">
         <v>-2.94597746349001</v>
       </c>
-      <c r="I65" s="1">
+      <c r="I65">
         <v>30.392156862745097</v>
       </c>
-      <c r="J65" s="1">
+      <c r="J65">
         <v>52</v>
       </c>
     </row>
     <row r="66" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E66" s="1">
+      <c r="E66">
         <v>17</v>
       </c>
-      <c r="F66" s="1">
+      <c r="F66">
         <v>49.056924349465049</v>
       </c>
-      <c r="G66" s="1">
+      <c r="G66">
         <v>9.9430756505349507</v>
       </c>
-      <c r="I66" s="1">
+      <c r="I66">
         <v>32.352941176470587</v>
       </c>
-      <c r="J66" s="1">
+      <c r="J66">
         <v>53</v>
       </c>
     </row>
     <row r="67" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E67" s="1">
+      <c r="E67">
         <v>18</v>
       </c>
-      <c r="F67" s="1">
+      <c r="F67">
         <v>63.224822704652354</v>
       </c>
-      <c r="G67" s="1">
+      <c r="G67">
         <v>0.77517729534764612</v>
       </c>
-      <c r="I67" s="1">
+      <c r="I67">
         <v>34.31372549019607</v>
       </c>
-      <c r="J67" s="1">
+      <c r="J67">
         <v>53</v>
       </c>
     </row>
     <row r="68" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E68" s="1">
+      <c r="E68">
         <v>19</v>
       </c>
-      <c r="F68" s="1">
+      <c r="F68">
         <v>50.94597746349001</v>
       </c>
-      <c r="G68" s="1">
+      <c r="G68">
         <v>-2.94597746349001</v>
       </c>
-      <c r="I68" s="1">
+      <c r="I68">
         <v>36.274509803921561</v>
       </c>
-      <c r="J68" s="1">
+      <c r="J68">
         <v>53</v>
       </c>
     </row>
     <row r="69" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E69" s="1">
+      <c r="E69">
         <v>20</v>
       </c>
-      <c r="F69" s="1">
+      <c r="F69">
         <v>53.779557134527494</v>
       </c>
-      <c r="G69" s="1">
+      <c r="G69">
         <v>1.2204428654725064</v>
       </c>
-      <c r="I69" s="1">
+      <c r="I69">
         <v>38.235294117647051</v>
       </c>
-      <c r="J69" s="1">
+      <c r="J69">
         <v>54</v>
       </c>
     </row>
     <row r="70" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E70" s="1">
+      <c r="E70">
         <v>21</v>
       </c>
-      <c r="F70" s="1">
+      <c r="F70">
         <v>57.557663362577443</v>
       </c>
-      <c r="G70" s="1">
+      <c r="G70">
         <v>20.442336637422557</v>
       </c>
-      <c r="I70" s="1">
+      <c r="I70">
         <v>40.196078431372541</v>
       </c>
-      <c r="J70" s="1">
+      <c r="J70">
         <v>55</v>
       </c>
     </row>
     <row r="71" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E71" s="1">
+      <c r="E71">
         <v>22</v>
       </c>
-      <c r="F71" s="1">
+      <c r="F71">
         <v>55.668610248552454</v>
       </c>
-      <c r="G71" s="1">
+      <c r="G71">
         <v>-10.668610248552454</v>
       </c>
-      <c r="I71" s="1">
+      <c r="I71">
         <v>42.156862745098032</v>
       </c>
-      <c r="J71" s="1">
+      <c r="J71">
         <v>55</v>
       </c>
     </row>
     <row r="72" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E72" s="1">
+      <c r="E72">
         <v>23</v>
       </c>
-      <c r="F72" s="1">
+      <c r="F72">
         <v>53.779557134527494</v>
       </c>
-      <c r="G72" s="1">
+      <c r="G72">
         <v>2.2204428654725064</v>
       </c>
-      <c r="I72" s="1">
+      <c r="I72">
         <v>44.117647058823522</v>
       </c>
-      <c r="J72" s="1">
+      <c r="J72">
         <v>55</v>
       </c>
     </row>
     <row r="73" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E73" s="1">
+      <c r="E73">
         <v>24</v>
       </c>
-      <c r="F73" s="1">
+      <c r="F73">
         <v>63.224822704652354</v>
       </c>
-      <c r="G73" s="1">
+      <c r="G73">
         <v>6.7751772953476461</v>
       </c>
-      <c r="I73" s="1">
+      <c r="I73">
         <v>46.078431372549012</v>
       </c>
-      <c r="J73" s="1">
+      <c r="J73">
         <v>55</v>
       </c>
     </row>
     <row r="74" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E74" s="1">
+      <c r="E74">
         <v>25</v>
       </c>
-      <c r="F74" s="1">
+      <c r="F74">
         <v>67.947455489714798</v>
       </c>
-      <c r="G74" s="1">
+      <c r="G74">
         <v>5.2544510285201795E-2</v>
       </c>
-      <c r="I74" s="1">
+      <c r="I74">
         <v>48.039215686274503</v>
       </c>
-      <c r="J74" s="1">
+      <c r="J74">
         <v>55</v>
       </c>
     </row>
     <row r="75" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E75" s="1">
+      <c r="E75">
         <v>26</v>
       </c>
-      <c r="F75" s="1">
+      <c r="F75">
         <v>60.391243033614899</v>
       </c>
-      <c r="G75" s="1">
+      <c r="G75">
         <v>-1.3912430336148986</v>
       </c>
-      <c r="I75" s="1">
+      <c r="I75">
         <v>49.999999999999993</v>
       </c>
-      <c r="J75" s="1">
+      <c r="J75">
         <v>56</v>
       </c>
     </row>
     <row r="76" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E76" s="1">
+      <c r="E76">
         <v>27</v>
       </c>
-      <c r="F76" s="1">
+      <c r="F76">
         <v>57.557663362577443</v>
       </c>
-      <c r="G76" s="1">
+      <c r="G76">
         <v>-2.5576633625774434</v>
       </c>
-      <c r="I76" s="1">
+      <c r="I76">
         <v>51.960784313725483</v>
       </c>
-      <c r="J76" s="1">
+      <c r="J76">
         <v>57</v>
       </c>
     </row>
     <row r="77" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E77" s="1">
+      <c r="E77">
         <v>28</v>
       </c>
-      <c r="F77" s="1">
+      <c r="F77">
         <v>67.002928932702332</v>
       </c>
-      <c r="G77" s="1">
+      <c r="G77">
         <v>-3.0029289327023321</v>
       </c>
-      <c r="I77" s="1">
+      <c r="I77">
         <v>53.921568627450974</v>
       </c>
-      <c r="J77" s="1">
+      <c r="J77">
         <v>57</v>
       </c>
     </row>
     <row r="78" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E78" s="1">
+      <c r="E78">
         <v>29</v>
       </c>
-      <c r="F78" s="1">
+      <c r="F78">
         <v>65.113875818677343</v>
       </c>
-      <c r="G78" s="1">
+      <c r="G78">
         <v>-6.113875818677343</v>
       </c>
-      <c r="I78" s="1">
+      <c r="I78">
         <v>55.882352941176464</v>
       </c>
-      <c r="J78" s="1">
+      <c r="J78">
         <v>58</v>
       </c>
     </row>
     <row r="79" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E79" s="1">
+      <c r="E79">
         <v>30</v>
       </c>
-      <c r="F79" s="1">
+      <c r="F79">
         <v>59.446716476602404</v>
       </c>
-      <c r="G79" s="1">
+      <c r="G79">
         <v>-4.4467164766024041</v>
       </c>
-      <c r="I79" s="1">
+      <c r="I79">
         <v>57.843137254901954</v>
       </c>
-      <c r="J79" s="1">
+      <c r="J79">
         <v>59</v>
       </c>
     </row>
     <row r="80" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E80" s="1">
+      <c r="E80">
         <v>31</v>
       </c>
-      <c r="F80" s="1">
+      <c r="F80">
         <v>43.38976500739011</v>
       </c>
-      <c r="G80" s="1">
+      <c r="G80">
         <v>-5.3897650073901104</v>
       </c>
-      <c r="I80" s="1">
+      <c r="I80">
         <v>59.803921568627445</v>
       </c>
-      <c r="J80" s="1">
+      <c r="J80">
         <v>59</v>
       </c>
     </row>
     <row r="81" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E81" s="1">
+      <c r="E81">
         <v>32</v>
       </c>
-      <c r="F81" s="1">
+      <c r="F81">
         <v>49.056924349465049</v>
       </c>
-      <c r="G81" s="1">
+      <c r="G81">
         <v>-4.0569243494650493</v>
       </c>
-      <c r="I81" s="1">
+      <c r="I81">
         <v>61.764705882352935</v>
       </c>
-      <c r="J81" s="1">
+      <c r="J81">
         <v>59</v>
       </c>
     </row>
     <row r="82" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E82" s="1">
+      <c r="E82">
         <v>33</v>
       </c>
-      <c r="F82" s="1">
+      <c r="F82">
         <v>50.94597746349001</v>
       </c>
-      <c r="G82" s="1">
+      <c r="G82">
         <v>-0.94597746349001</v>
       </c>
-      <c r="I82" s="1">
+      <c r="I82">
         <v>63.725490196078425</v>
       </c>
-      <c r="J82" s="1">
+      <c r="J82">
         <v>59</v>
       </c>
     </row>
     <row r="83" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E83" s="1">
+      <c r="E83">
         <v>34</v>
       </c>
-      <c r="F83" s="1">
+      <c r="F83">
         <v>50.94597746349001</v>
       </c>
-      <c r="G83" s="1">
+      <c r="G83">
         <v>-4.94597746349001</v>
       </c>
-      <c r="I83" s="1">
+      <c r="I83">
         <v>65.686274509803923</v>
       </c>
-      <c r="J83" s="1">
+      <c r="J83">
         <v>61</v>
       </c>
     </row>
     <row r="84" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E84" s="1">
+      <c r="E84">
         <v>35</v>
       </c>
-      <c r="F84" s="1">
+      <c r="F84">
         <v>50.001450906477544</v>
       </c>
-      <c r="G84" s="1">
+      <c r="G84">
         <v>-1.4509064775438674E-3</v>
       </c>
-      <c r="I84" s="1">
+      <c r="I84">
         <v>67.647058823529406</v>
       </c>
-      <c r="J84" s="1">
+      <c r="J84">
         <v>63</v>
       </c>
     </row>
     <row r="85" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E85" s="1">
+      <c r="E85">
         <v>36</v>
       </c>
-      <c r="F85" s="1">
+      <c r="F85">
         <v>69.836508603739787</v>
       </c>
-      <c r="G85" s="1">
+      <c r="G85">
         <v>-6.8365086037397873</v>
       </c>
-      <c r="I85" s="1">
+      <c r="I85">
         <v>69.607843137254903</v>
       </c>
-      <c r="J85" s="1">
+      <c r="J85">
         <v>64</v>
       </c>
     </row>
     <row r="86" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E86" s="1">
+      <c r="E86">
         <v>37</v>
       </c>
-      <c r="F86" s="1">
+      <c r="F86">
         <v>59.446716476602404</v>
       </c>
-      <c r="G86" s="1">
+      <c r="G86">
         <v>11.553283523397596</v>
       </c>
-      <c r="I86" s="1">
+      <c r="I86">
         <v>71.568627450980387</v>
       </c>
-      <c r="J86" s="1">
+      <c r="J86">
         <v>64</v>
       </c>
     </row>
     <row r="87" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E87" s="1">
+      <c r="E87">
         <v>38</v>
       </c>
-      <c r="F87" s="1">
+      <c r="F87">
         <v>52.835030577514999</v>
       </c>
-      <c r="G87" s="1">
+      <c r="G87">
         <v>-0.8350305775149991</v>
       </c>
-      <c r="I87" s="1">
+      <c r="I87">
         <v>73.529411764705884</v>
       </c>
-      <c r="J87" s="1">
+      <c r="J87">
         <v>65</v>
       </c>
     </row>
     <row r="88" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E88" s="1">
+      <c r="E88">
         <v>39</v>
       </c>
-      <c r="F88" s="1">
+      <c r="F88">
         <v>67.947455489714798</v>
       </c>
-      <c r="G88" s="1">
+      <c r="G88">
         <v>6.0525445102852018</v>
       </c>
-      <c r="I88" s="1">
+      <c r="I88">
         <v>75.490196078431367</v>
       </c>
-      <c r="J88" s="1">
+      <c r="J88">
         <v>65</v>
       </c>
     </row>
     <row r="89" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E89" s="1">
+      <c r="E89">
         <v>40</v>
       </c>
-      <c r="F89" s="1">
+      <c r="F89">
         <v>63.224822704652354</v>
       </c>
-      <c r="G89" s="1">
+      <c r="G89">
         <v>-11.224822704652354</v>
       </c>
-      <c r="I89" s="1">
+      <c r="I89">
         <v>77.450980392156865</v>
       </c>
-      <c r="J89" s="1">
+      <c r="J89">
         <v>68</v>
       </c>
     </row>
     <row r="90" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E90" s="1">
+      <c r="E90">
         <v>41</v>
       </c>
-      <c r="F90" s="1">
+      <c r="F90">
         <v>63.224822704652354</v>
       </c>
-      <c r="G90" s="1">
+      <c r="G90">
         <v>-2.2248227046523539</v>
       </c>
-      <c r="I90" s="1">
+      <c r="I90">
         <v>79.411764705882348</v>
       </c>
-      <c r="J90" s="1">
+      <c r="J90">
         <v>68</v>
       </c>
     </row>
     <row r="91" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E91" s="1">
+      <c r="E91">
         <v>42</v>
       </c>
-      <c r="F91" s="1">
+      <c r="F91">
         <v>61.335769590627393</v>
       </c>
-      <c r="G91" s="1">
+      <c r="G91">
         <v>3.6642304093726068</v>
       </c>
-      <c r="I91" s="1">
+      <c r="I91">
         <v>81.372549019607845</v>
       </c>
-      <c r="J91" s="1">
+      <c r="J91">
         <v>70</v>
       </c>
     </row>
     <row r="92" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E92" s="1">
+      <c r="E92">
         <v>43</v>
       </c>
-      <c r="F92" s="1">
+      <c r="F92">
         <v>61.335769590627393</v>
       </c>
-      <c r="G92" s="1">
+      <c r="G92">
         <v>6.6642304093726068</v>
       </c>
-      <c r="I92" s="1">
+      <c r="I92">
         <v>83.333333333333329</v>
       </c>
-      <c r="J92" s="1">
+      <c r="J92">
         <v>71</v>
       </c>
     </row>
     <row r="93" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E93" s="1">
+      <c r="E93">
         <v>44</v>
       </c>
-      <c r="F93" s="1">
+      <c r="F93">
         <v>60.391243033614899</v>
       </c>
-      <c r="G93" s="1">
+      <c r="G93">
         <v>-3.3912430336148986</v>
       </c>
-      <c r="I93" s="1">
+      <c r="I93">
         <v>85.294117647058826</v>
       </c>
-      <c r="J93" s="1">
+      <c r="J93">
         <v>71</v>
       </c>
     </row>
     <row r="94" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E94" s="1">
+      <c r="E94">
         <v>45</v>
       </c>
-      <c r="F94" s="1">
+      <c r="F94">
         <v>50.94597746349001</v>
       </c>
-      <c r="G94" s="1">
+      <c r="G94">
         <v>-3.94597746349001</v>
       </c>
-      <c r="I94" s="1">
+      <c r="I94">
         <v>87.254901960784309</v>
       </c>
-      <c r="J94" s="1">
+      <c r="J94">
         <v>73</v>
       </c>
     </row>
     <row r="95" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E95" s="1">
+      <c r="E95">
         <v>46</v>
       </c>
-      <c r="F95" s="1">
+      <c r="F95">
         <v>57.557663362577443</v>
       </c>
-      <c r="G95" s="1">
+      <c r="G95">
         <v>-9.5576633625774434</v>
       </c>
-      <c r="I95" s="1">
+      <c r="I95">
         <v>89.215686274509807</v>
       </c>
-      <c r="J95" s="1">
+      <c r="J95">
         <v>73</v>
       </c>
     </row>
     <row r="96" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E96" s="1">
+      <c r="E96">
         <v>47</v>
       </c>
-      <c r="F96" s="1">
+      <c r="F96">
         <v>58.502189919589938</v>
       </c>
-      <c r="G96" s="1">
+      <c r="G96">
         <v>-0.50218991958993797</v>
       </c>
-      <c r="I96" s="1">
+      <c r="I96">
         <v>91.17647058823529</v>
       </c>
-      <c r="J96" s="1">
+      <c r="J96">
         <v>74</v>
       </c>
     </row>
     <row r="97" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E97" s="1">
+      <c r="E97">
         <v>48</v>
       </c>
-      <c r="F97" s="1">
+      <c r="F97">
         <v>56.613136805564949</v>
       </c>
-      <c r="G97" s="1">
+      <c r="G97">
         <v>2.3868631944350511</v>
       </c>
-      <c r="I97" s="1">
+      <c r="I97">
         <v>93.137254901960787</v>
       </c>
-      <c r="J97" s="1">
+      <c r="J97">
         <v>74</v>
       </c>
     </row>
     <row r="98" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E98" s="1">
+      <c r="E98">
         <v>49</v>
       </c>
-      <c r="F98" s="1">
+      <c r="F98">
         <v>54.724083691539988</v>
       </c>
-      <c r="G98" s="1">
+      <c r="G98">
         <v>0.27591630846001181</v>
       </c>
-      <c r="I98" s="1">
+      <c r="I98">
         <v>95.098039215686271</v>
       </c>
-      <c r="J98" s="1">
+      <c r="J98">
         <v>74</v>
       </c>
     </row>
     <row r="99" spans="5:10" x14ac:dyDescent="0.45">
-      <c r="E99" s="1">
+      <c r="E99">
         <v>50</v>
       </c>
-      <c r="F99" s="1">
+      <c r="F99">
         <v>63.224822704652354</v>
       </c>
-      <c r="G99" s="1">
+      <c r="G99">
         <v>10.775177295347646</v>
       </c>
-      <c r="I99" s="1">
+      <c r="I99">
         <v>97.058823529411768</v>
       </c>
-      <c r="J99" s="1">
+      <c r="J99">
         <v>78</v>
       </c>
     </row>
     <row r="100" spans="5:10" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="E100" s="2">
+      <c r="E100" s="1">
         <v>51</v>
       </c>
-      <c r="F100" s="2">
+      <c r="F100" s="1">
         <v>69.836508603739787</v>
       </c>
-      <c r="G100" s="2">
+      <c r="G100" s="1">
         <v>4.1634913962602127</v>
       </c>
-      <c r="I100" s="2">
+      <c r="I100" s="1">
         <v>99.019607843137251</v>
       </c>
-      <c r="J100" s="2">
+      <c r="J100" s="1">
         <v>78</v>
       </c>
     </row>
